--- a/FINAL_OUTPUT.xlsx
+++ b/FINAL_OUTPUT.xlsx
@@ -24346,7 +24346,7 @@
         <v>94.29000000000001</v>
       </c>
       <c r="Q169">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="R169">
         <v>100</v>
@@ -31626,10 +31626,10 @@
         <v>86.23</v>
       </c>
       <c r="Q299">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R299">
-        <v>97.48</v>
+        <v>96.64</v>
       </c>
     </row>
     <row r="300" spans="1:18">
@@ -34370,10 +34370,10 @@
         <v>93.33</v>
       </c>
       <c r="Q348">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R348">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="349" spans="1:18">
@@ -37058,10 +37058,10 @@
         <v>100</v>
       </c>
       <c r="Q396">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="R396">
-        <v>95.70999999999999</v>
+        <v>90</v>
       </c>
     </row>
     <row r="397" spans="1:18">
@@ -37842,10 +37842,10 @@
         <v>99.29000000000001</v>
       </c>
       <c r="Q410">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R410">
-        <v>98.56</v>
+        <v>97.84</v>
       </c>
     </row>
     <row r="411" spans="1:18">
@@ -43890,10 +43890,10 @@
         <v>95</v>
       </c>
       <c r="Q518">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="R518">
-        <v>96.98999999999999</v>
+        <v>96.23999999999999</v>
       </c>
     </row>
     <row r="519" spans="1:18">
@@ -45794,10 +45794,10 @@
         <v>82.01000000000001</v>
       </c>
       <c r="Q552">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="R552">
-        <v>85.95999999999999</v>
+        <v>83.33</v>
       </c>
     </row>
     <row r="553" spans="1:18">
@@ -50610,10 +50610,10 @@
         <v>83.33</v>
       </c>
       <c r="Q638">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="R638">
-        <v>97.39</v>
+        <v>96.52</v>
       </c>
     </row>
     <row r="639" spans="1:18">
@@ -57778,10 +57778,10 @@
         <v>93.70999999999999</v>
       </c>
       <c r="Q766">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="R766">
-        <v>79.88</v>
+        <v>79.27</v>
       </c>
     </row>
     <row r="767" spans="1:18">
@@ -64050,10 +64050,10 @@
         <v>87.86</v>
       </c>
       <c r="Q878">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="R878">
-        <v>99.19</v>
+        <v>97.56</v>
       </c>
     </row>
     <row r="879" spans="1:18">
@@ -67186,10 +67186,10 @@
         <v>94.70999999999999</v>
       </c>
       <c r="Q934">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="R934">
-        <v>98.76000000000001</v>
+        <v>96.27</v>
       </c>
     </row>
     <row r="935" spans="1:18">
@@ -74578,10 +74578,10 @@
         <v>83.56999999999999</v>
       </c>
       <c r="Q1066">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="R1066">
-        <v>91.45</v>
+        <v>80.34</v>
       </c>
     </row>
     <row r="1067" spans="1:18">
@@ -75698,10 +75698,10 @@
         <v>88.56999999999999</v>
       </c>
       <c r="Q1086">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="R1086">
-        <v>36.29</v>
+        <v>34.68</v>
       </c>
     </row>
     <row r="1087" spans="1:18">
@@ -76202,10 +76202,10 @@
         <v>100</v>
       </c>
       <c r="Q1095">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="R1095">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="1096" spans="1:18">
@@ -76258,10 +76258,10 @@
         <v>97.18000000000001</v>
       </c>
       <c r="Q1096">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="R1096">
-        <v>85.51000000000001</v>
+        <v>83.33</v>
       </c>
     </row>
     <row r="1097" spans="1:18">
